--- a/San_Antonio_Spurs_2025-26_stats.xlsx
+++ b/San_Antonio_Spurs_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1261,6 +1261,72 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>11</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>14</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1275,7 +1341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2103,6 +2169,72 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2117,7 +2249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2945,6 +3077,72 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2959,7 +3157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3787,6 +3985,72 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3823,7 +4087,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.18181818181818</v>
+        <v>26.16666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -3833,7 +4097,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.33333333333333</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="4">
@@ -3843,7 +4107,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.90909090909091</v>
+        <v>18.41666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -3863,7 +4127,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.90909090909091</v>
+        <v>13.66666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -3873,7 +4137,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.81818181818182</v>
+        <v>11.41666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -3883,7 +4147,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11.45454545454546</v>
+        <v>10.83333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3893,7 +4157,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="10">
@@ -3903,7 +4167,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.181818181818182</v>
+        <v>9.583333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -3913,7 +4177,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5.833333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -4029,7 +4293,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.909090909090909</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="3">
@@ -4039,7 +4303,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.333333333333333</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="4">
@@ -4069,23 +4333,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.090909090909091</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4095,47 +4359,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kelly Olynyk</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.666666666666667</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Kelly Olynyk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.636363636363636</v>
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Jeremy Sochan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.454545454545455</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jeremy Sochan</t>
+          <t>David Jones Garcia</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.4</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>David Jones Garcia</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4235,7 +4499,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>12.91666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -4245,27 +4509,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.090909090909091</v>
+        <v>6.333333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Luke Kornet</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.75</v>
+        <v>5.666666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Luke Kornet</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.727272727272728</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -4275,7 +4539,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.090909090909091</v>
+        <v>4.833333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -4305,7 +4569,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.636363636363636</v>
+        <v>3.583333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -4315,7 +4579,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.727272727272727</v>
+        <v>2.833333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -4325,7 +4589,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -4441,7 +4705,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.818181818181818</v>
+        <v>2.666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -4451,43 +4715,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.545454545454545</v>
+        <v>2.416666666666667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.818181818181818</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.545454545454545</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.333333333333333</v>
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Lindy Waters III</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4497,11 +4761,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lindy Waters III</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="9">
@@ -4517,21 +4781,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Jordan McLaughlin</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jordan McLaughlin</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.625</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="12">
@@ -4541,7 +4805,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -4625,7 +4889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4886,6 +5150,27 @@
         <v>245</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>108</v>
+      </c>
+      <c r="D13" t="n">
+        <v>109</v>
+      </c>
+      <c r="E13" t="n">
+        <v>217</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
